--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121149729</v>
+        <v>121149727</v>
       </c>
       <c r="B12" t="n">
-        <v>90707</v>
+        <v>91988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693808</v>
+        <v>693793</v>
       </c>
       <c r="R12" t="n">
-        <v>7318680</v>
+        <v>7318620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121149727</v>
+        <v>121149729</v>
       </c>
       <c r="B13" t="n">
-        <v>91988</v>
+        <v>90707</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693793</v>
+        <v>693808</v>
       </c>
       <c r="R13" t="n">
-        <v>7318620</v>
+        <v>7318680</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>121149727</v>
       </c>
       <c r="B12" t="n">
-        <v>91988</v>
+        <v>91998</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>121149729</v>
       </c>
       <c r="B13" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121149727</v>
+        <v>121149729</v>
       </c>
       <c r="B12" t="n">
-        <v>91998</v>
+        <v>90717</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693793</v>
+        <v>693808</v>
       </c>
       <c r="R12" t="n">
-        <v>7318620</v>
+        <v>7318680</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121149729</v>
+        <v>121149727</v>
       </c>
       <c r="B13" t="n">
-        <v>90717</v>
+        <v>91998</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693808</v>
+        <v>693793</v>
       </c>
       <c r="R13" t="n">
-        <v>7318680</v>
+        <v>7318620</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>121149729</v>
       </c>
       <c r="B12" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>121149727</v>
       </c>
       <c r="B13" t="n">
-        <v>91998</v>
+        <v>92010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1738,7 +1738,7 @@
         <v>121149729</v>
       </c>
       <c r="B12" t="n">
-        <v>90729</v>
+        <v>90730</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>121149727</v>
       </c>
       <c r="B13" t="n">
-        <v>92010</v>
+        <v>92011</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121149729</v>
+        <v>121149727</v>
       </c>
       <c r="B12" t="n">
-        <v>90730</v>
+        <v>92014</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693808</v>
+        <v>693793</v>
       </c>
       <c r="R12" t="n">
-        <v>7318680</v>
+        <v>7318620</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121149727</v>
+        <v>121149729</v>
       </c>
       <c r="B13" t="n">
-        <v>92011</v>
+        <v>90733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693793</v>
+        <v>693808</v>
       </c>
       <c r="R13" t="n">
-        <v>7318620</v>
+        <v>7318680</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>

--- a/artfynd/A 53150-2022 artfynd.xlsx
+++ b/artfynd/A 53150-2022 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121149727</v>
+        <v>121149729</v>
       </c>
       <c r="B12" t="n">
-        <v>92014</v>
+        <v>90733</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>693793</v>
+        <v>693808</v>
       </c>
       <c r="R12" t="n">
-        <v>7318620</v>
+        <v>7318680</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121149729</v>
+        <v>121149727</v>
       </c>
       <c r="B13" t="n">
-        <v>90733</v>
+        <v>92014</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1862,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>3100</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>693808</v>
+        <v>693793</v>
       </c>
       <c r="R13" t="n">
-        <v>7318680</v>
+        <v>7318620</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
